--- a/static/migration_templates/03_users.xlsx
+++ b/static/migration_templates/03_users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,33 +529,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>PostgreSQL table</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Login users. role: Admin, Staff, Member. password is hashed on import.</t>
+          <t>users</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Required columns</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>username, password</t>
+          <t>Login users (users table). role: PlatformAdmin, Admin, Staff, or Member. password is hashed on import (stored as password_hash). PlatformAdmin accounts are never deleted by replace mode.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>Required columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>username, password</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Paste your data starting row 2 on the main sheet. Do not rename header row.</t>
         </is>

--- a/static/migration_templates/03_users.xlsx
+++ b/static/migration_templates/03_users.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
